--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         <v>22866.5</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>16.53000068664551</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>22866.5</v>
@@ -15750,7 +15750,7 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.2</v>
@@ -30721,7 +30721,7 @@
         <v>-0.37</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>-0.37</v>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3.71</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>22840.55078125</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.47999954223633</v>
+        <v>16.32999992370605</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>22840.55078125</v>
@@ -804,7 +804,7 @@
         <v>22654.650390625</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>16.22999954223633</v>
+        <v>16.32999992370605</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>22654.650390625</v>
@@ -14610,7 +14610,7 @@
         <v>0.09</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>3.71</v>
+        <v>2.77</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.09</v>
@@ -14642,7 +14642,7 @@
         <v>-0.72</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.14</v>
+        <v>2.77</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-0.72</v>
@@ -28460,7 +28460,7 @@
         <v>0.82</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.82</v>
@@ -28492,7 +28492,7 @@
         <v>0.54</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.54</v>
@@ -42230,12 +42230,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 150, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -42250,7 +42250,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2.77</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>22840.55078125</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.32999992370605</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>22840.55078125</v>
@@ -14610,7 +14610,7 @@
         <v>0.09</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.77</v>
+        <v>3.71</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.09</v>
@@ -28460,7 +28460,7 @@
         <v>0.82</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.82</v>
@@ -42230,12 +42230,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>10.08</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7.25</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5.21</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3.52</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-1.74</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-2.23</v>
+        <v>-1.66</v>
       </c>
     </row>
   </sheetData>
@@ -748,34 +748,34 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>23329</v>
+        <v>23446.80078125</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>71804.046875</v>
+        <v>72462.3984375</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>24469.75</v>
+        <v>24612.25</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13613.400390625</v>
+        <v>13695.9501953125</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>17878.599609375</v>
+        <v>17979.650390625</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>22787.19921875</v>
+        <v>22928.849609375</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>22794.19921875</v>
+        <v>22935.099609375</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.45000076293945</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>22794.19921875</v>
+        <v>22935.099609375</v>
       </c>
     </row>
     <row r="3">
@@ -804,7 +804,7 @@
         <v>22860.05078125</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>16.47999954223633</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>22860.05078125</v>
@@ -14650,34 +14650,34 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-1.74</v>
+        <v>-1.25</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>5.21</v>
+        <v>6.18</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-2.23</v>
+        <v>-1.66</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>10.08</v>
+        <v>10.7</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7.25</v>
+        <v>7.92</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>3.52</v>
+        <v>4.03</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="3">
@@ -14706,7 +14706,7 @@
         <v>0.18</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.18</v>
@@ -28564,34 +28564,34 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.39</v>
+        <v>0.53</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.37</v>
+        <v>0.21</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.13</v>
+        <v>0.49</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.29</v>
+        <v>0.33</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-0.18</v>
+        <v>0.24</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-0.29</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="3">
@@ -28620,7 +28620,7 @@
         <v>0.09</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.09</v>
@@ -42418,16 +42418,16 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>7.86</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4.59</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-2.86</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-3.25</v>
+        <v>-2.88</v>
       </c>
     </row>
   </sheetData>
@@ -751,31 +751,31 @@
         <v>46290</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>23063.099609375</v>
+        <v>23140.5</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>71381.453125</v>
+        <v>71778.6484375</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>24216.19921875</v>
+        <v>24307.55078125</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13457.5498046875</v>
+        <v>13494.2001953125</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>17518.05078125</v>
+        <v>17474.099609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>22469.900390625</v>
+        <v>22437</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>22552.599609375</v>
+        <v>22603.5</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.53000068664551</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>22552.599609375</v>
+        <v>22603.5</v>
       </c>
     </row>
     <row r="3">
@@ -804,7 +804,7 @@
         <v>22552.599609375</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>16.53000068664551</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>22552.599609375</v>
@@ -14749,31 +14749,31 @@
         <v>46290</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-2.86</v>
+        <v>-2.54</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.59</v>
+        <v>5.17</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-3.25</v>
+        <v>-2.88</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>7.86</v>
+        <v>7.59</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="3">
@@ -14802,7 +14802,7 @@
         <v>-1.17</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-1.17</v>
@@ -28759,31 +28759,31 @@
         <v>46290</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="3">
@@ -28812,7 +28812,7 @@
         <v>-1.67</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-1.67</v>
@@ -42710,12 +42710,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>22603.5</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.30999946594238</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>22603.5</v>
@@ -14770,7 +14770,7 @@
         <v>-0.95</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>-0.95</v>
@@ -28780,7 +28780,7 @@
         <v>0.23</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.23</v>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-1.79%</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-2.17</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-4.73</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-5.17</v>
+        <v>-6.04</v>
       </c>
     </row>
   </sheetData>
@@ -751,31 +751,31 @@
         <v>46296</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>22620.44921875</v>
+        <v>22421.94921875</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>69746.953125</v>
+        <v>68981.3515625</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>23734.69921875</v>
+        <v>23516.5</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13169.9501953125</v>
+        <v>13046.4501953125</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>17028.69921875</v>
+        <v>16840.349609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>21867.5</v>
+        <v>21643.849609375</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>22072.099609375</v>
+        <v>21857.75</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>15.96000003814697</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>22072.099609375</v>
+        <v>21857.75</v>
       </c>
     </row>
     <row r="3">
@@ -804,7 +804,7 @@
         <v>22072.099609375</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>15.96000003814697</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>22072.099609375</v>
@@ -14877,31 +14877,31 @@
         <v>46296</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-4.73</v>
+        <v>-5.56</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-5.17</v>
+        <v>-6.04</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-2.17</v>
+        <v>-3.09</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="3">
@@ -14930,7 +14930,7 @@
         <v>-3.28</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-3.28</v>
@@ -29015,31 +29015,31 @@
         <v>46296</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="3">
@@ -29068,7 +29068,7 @@
         <v>-0.13</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-0.13</v>
@@ -43094,12 +43094,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -43109,7 +43109,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.14%</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.38</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.31</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-0.93</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-4.19</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-6.36</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-7.04</v>
+        <v>-5.92</v>
       </c>
     </row>
   </sheetData>
@@ -751,31 +751,31 @@
         <v>46304</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>22231.80078125</v>
+        <v>22520.44921875</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>67614.5</v>
+        <v>68166.703125</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>23266.75</v>
+        <v>23547.900390625</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>12897.7998046875</v>
+        <v>13062.849609375</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>16530.900390625</v>
+        <v>16786.69921875</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>21311.5</v>
+        <v>21603.25</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>21616.150390625</v>
+        <v>21866.650390625</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>15.94999980926514</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>21616.150390625</v>
+        <v>21866.650390625</v>
       </c>
     </row>
     <row r="3">
@@ -804,7 +804,7 @@
         <v>21616.150390625</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>15.94999980926514</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>21616.150390625</v>
@@ -14909,31 +14909,31 @@
         <v>46304</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-6.36</v>
+        <v>-5.15</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.93</v>
+        <v>-0.12</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-7.04</v>
+        <v>-5.92</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-4.19</v>
+        <v>-2.97</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.31</v>
+        <v>1.68</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.38</v>
+        <v>-1.76</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="3">
@@ -14962,7 +14962,7 @@
         <v>-5.27</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.38</v>
+        <v>-1.76</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-5.27</v>
@@ -29079,31 +29079,31 @@
         <v>46304</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="3">
@@ -29132,7 +29132,7 @@
         <v>-2.01</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>-2.13</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-2.01</v>
@@ -43190,12 +43190,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty Next 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -43205,7 +43205,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-2.03%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-1.76</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>21866.650390625</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>15.60999965667725</v>
+        <v>15.77000045776367</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>21866.650390625</v>
@@ -14930,7 +14930,7 @@
         <v>-4.18</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-1.76</v>
+        <v>-0.76</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>-4.18</v>
@@ -29100,7 +29100,7 @@
         <v>1.16</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>1.16</v>
@@ -43195,7 +43195,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Next 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.42%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>22270.05078125</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>22270.05078125</v>
@@ -804,7 +804,7 @@
         <v>22180.80078125</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>15.89999961853027</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>22180.80078125</v>
@@ -15090,7 +15090,7 @@
         <v>-2.41</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>-2.41</v>
@@ -15122,7 +15122,7 @@
         <v>-2.8</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-2.8</v>
@@ -29420,7 +29420,7 @@
         <v>0.4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.4</v>
@@ -29452,7 +29452,7 @@
         <v>0.65</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.65</v>
@@ -43670,12 +43670,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.31</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>22270.05078125</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>15.9399995803833</v>
+        <v>16</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>22270.05078125</v>
@@ -15090,7 +15090,7 @@
         <v>-2.41</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>-2.41</v>
@@ -29420,7 +29420,7 @@
         <v>0.4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.4</v>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-1.34%</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4.34</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2.31</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.09</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.93</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-2.51</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-3.58</v>
+        <v>-4.53</v>
       </c>
     </row>
   </sheetData>
@@ -751,31 +751,31 @@
         <v>46314</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>23146.150390625</v>
+        <v>22888.94921875</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>68988.6015625</v>
+        <v>68695.8515625</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>24133.099609375</v>
+        <v>23895.44921875</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13337.400390625</v>
+        <v>13203.349609375</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>16946.30078125</v>
+        <v>16767.849609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>21736.75</v>
+        <v>21499.30078125</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>22270.05078125</v>
+        <v>22041.599609375</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16</v>
+        <v>15.84000015258789</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>22270.05078125</v>
+        <v>22041.599609375</v>
       </c>
     </row>
     <row r="3">
@@ -15101,31 +15101,31 @@
         <v>46314</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-2.51</v>
+        <v>-3.6</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1.09</v>
+        <v>0.66</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-3.58</v>
+        <v>-4.53</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.93</v>
+        <v>-1.92</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4.34</v>
+        <v>3.24</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2.31</v>
+        <v>1.19</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.31</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="3">
@@ -29463,31 +29463,31 @@
         <v>46314</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="3">
@@ -43766,12 +43766,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty 50, Nifty Midcap 150, Nifty Midcap 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.36%</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1.04</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-1.03</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-1.31</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-2.58</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-3.25</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-4.44</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-5.56</v>
+        <v>-6.25</v>
       </c>
     </row>
   </sheetData>
@@ -751,31 +751,31 @@
         <v>46318</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>22687.650390625</v>
+        <v>22600</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>67354.1484375</v>
+        <v>65828.6015625</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>23637.80078125</v>
+        <v>23465.05078125</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13025.5</v>
+        <v>12892.400390625</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>16410.80078125</v>
+        <v>16066.400390625</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>21028.650390625</v>
+        <v>20592.75</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>21696.55078125</v>
+        <v>21427.599609375</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>15.47999954223633</v>
+        <v>15.25</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>21696.55078125</v>
+        <v>21427.599609375</v>
       </c>
     </row>
     <row r="3">
@@ -15197,31 +15197,31 @@
         <v>46318</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-4.44</v>
+        <v>-4.81</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-1.31</v>
+        <v>-3.54</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-5.56</v>
+        <v>-6.25</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-3.25</v>
+        <v>-4.23</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.04</v>
+        <v>-1.08</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-1.03</v>
+        <v>-3.08</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-2.58</v>
+        <v>-4.03</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="3">
@@ -29655,31 +29655,31 @@
         <v>46318</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-2.26</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-2.07</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>-1.24</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="3">
@@ -44054,12 +44054,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -50879,7 +50879,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
